--- a/results/link-prediction-gcn/Link/3shot/PROTEINS/GCN_total_results.xlsx
+++ b/results/link-prediction-gcn/Link/3shot/PROTEINS/GCN_total_results.xlsx
@@ -893,457 +893,457 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.4854±0.0000</t>
+          <t>0.4854±0.0002</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.5151±0.0000</t>
+          <t>0.5167±0.0016</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.5146±0.0000</t>
+          <t>0.5146±0.0001</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.5146±0.0000</t>
+          <t>0.5146±0.0003</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0.5147±0.0000</t>
+          <t>0.5231±0.0115</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0.5146±0.0000</t>
+          <t>0.5255±0.0148</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.5146±0.0000</t>
+          <t>0.5204±0.0067</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.5146±0.0000</t>
+          <t>0.5145±0.0003</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0.5146±0.0000</t>
+          <t>0.5145±0.0003</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0.5146±0.0000</t>
+          <t>0.5145±0.0003</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0.5146±0.0000</t>
+          <t>0.5146±0.0001</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>0.5410±0.0000</t>
+          <t>0.5354±0.0146</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>0.5146±0.0000</t>
+          <t>0.5149±0.0004</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0.4854±0.0000</t>
+          <t>0.4854±0.0002</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>0.5146±0.0000</t>
+          <t>0.5242±0.0124</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>0.5217±0.0000</t>
+          <t>0.5232±0.0095</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>0.5148±0.0000</t>
+          <t>0.5141±0.0032</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>0.5238±0.0000</t>
+          <t>0.5205±0.0057</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>0.5146±0.0000</t>
+          <t>0.5230±0.0074</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>0.5147±0.0000</t>
+          <t>0.5152±0.0007</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>0.5151±0.0000</t>
+          <t>0.5154±0.0008</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0.5151±0.0000</t>
+          <t>0.5154±0.0008</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>0.5151±0.0000</t>
+          <t>0.5154±0.0008</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>0.5146±0.0000</t>
+          <t>0.5217±0.0101</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0.5146±0.0000</t>
+          <t>0.5146±0.0002</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.5144±0.0000</t>
+          <t>0.5166±0.0017</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>0.4856±0.0000</t>
+          <t>0.4854±0.0009</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>0.5117±0.0000</t>
+          <t>0.5263±0.0024</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>0.5149±0.0000</t>
+          <t>0.5389±0.0171</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>0.5145±0.0000</t>
+          <t>0.5390±0.0218</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.5177±0.0000</t>
+          <t>0.5239±0.0011</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.5235±0.0000</t>
+          <t>0.5268±0.0101</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.5142±0.0000</t>
+          <t>0.5172±0.0011</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>0.5229±0.0000</t>
+          <t>0.5314±0.0091</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>0.5229±0.0000</t>
+          <t>0.5314±0.0091</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>0.5229±0.0000</t>
+          <t>0.5314±0.0091</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>0.5162±0.0000</t>
+          <t>0.5176±0.0046</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>0.5619±0.0000</t>
+          <t>0.5640±0.0038</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>0.5214±0.0000</t>
+          <t>0.5245±0.0063</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>0.4854±0.0000</t>
+          <t>0.4857±0.0003</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>0.5511±0.0000</t>
+          <t>0.5469±0.0080</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.5144±0.0000</t>
+          <t>0.5479±0.0025</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.5154±0.0000</t>
+          <t>0.5182±0.0069</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>0.5406±0.0000</t>
+          <t>0.5502±0.0057</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>0.5364±0.0000</t>
+          <t>0.5370±0.0100</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>0.5520±0.0000</t>
+          <t>0.5476±0.0038</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>0.5318±0.0000</t>
+          <t>0.5449±0.0105</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>0.5318±0.0000</t>
+          <t>0.5449±0.0105</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>0.5318±0.0000</t>
+          <t>0.5449±0.0105</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>0.5496±0.0000</t>
+          <t>0.5416±0.0033</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>0.5379±0.0000</t>
+          <t>0.5198±0.0013</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>0.5261±0.0000</t>
+          <t>0.5511±0.0087</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>0.4854±0.0000</t>
+          <t>0.4854±0.0002</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>0.5146±0.0000</t>
+          <t>0.5156±0.0014</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>0.5146±0.0000</t>
+          <t>0.5146±0.0001</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>0.5145±0.0000</t>
+          <t>0.5262±0.0158</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>0.5148±0.0000</t>
+          <t>0.5167±0.0026</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>0.5148±0.0000</t>
+          <t>0.5174±0.0037</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>0.5150±0.0000</t>
+          <t>0.5151±0.0009</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>0.5148±0.0000</t>
+          <t>0.5167±0.0010</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>0.5148±0.0000</t>
+          <t>0.5167±0.0010</t>
         </is>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>0.5148±0.0000</t>
+          <t>0.5167±0.0010</t>
         </is>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>0.5150±0.0000</t>
+          <t>0.5146±0.0005</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>0.5145±0.0000</t>
+          <t>0.5146±0.0002</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>0.5148±0.0000</t>
+          <t>0.5207±0.0077</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>0.4854±0.0000</t>
+          <t>0.4854±0.0002</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>0.5146±0.0000</t>
+          <t>0.5228±0.0034</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>0.5146±0.0000</t>
+          <t>0.5146±0.0002</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>0.5145±0.0000</t>
+          <t>0.5178±0.0045</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>0.5147±0.0000</t>
+          <t>0.5145±0.0004</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>0.5146±0.0000</t>
+          <t>0.5154±0.0010</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>0.5150±0.0000</t>
+          <t>0.5172±0.0039</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>0.5146±0.0000</t>
+          <t>0.5238±0.0068</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
         <is>
-          <t>0.5146±0.0000</t>
+          <t>0.5237±0.0068</t>
         </is>
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>0.5146±0.0000</t>
+          <t>0.5237±0.0068</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>0.5150±0.0000</t>
+          <t>0.5158±0.0015</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>0.5146±0.0000</t>
+          <t>0.5175±0.0048</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
         <is>
-          <t>0.5146±0.0000</t>
+          <t>0.5172±0.0040</t>
         </is>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>0.4854±0.0000</t>
+          <t>0.4854±0.0002</t>
         </is>
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>0.5157±0.0000</t>
+          <t>0.5207±0.0043</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>0.5139±0.0000</t>
+          <t>0.5247±0.0132</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>0.5147±0.0000</t>
+          <t>0.5193±0.0045</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>0.5166±0.0000</t>
+          <t>0.5179±0.0031</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>0.5160±0.0000</t>
+          <t>0.5170±0.0027</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>0.5128±0.0000</t>
+          <t>0.5169±0.0042</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>0.5148±0.0000</t>
+          <t>0.5144±0.0004</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
         <is>
-          <t>0.5148±0.0000</t>
+          <t>0.5144±0.0004</t>
         </is>
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>0.5148±0.0000</t>
+          <t>0.5144±0.0004</t>
         </is>
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>0.5282±0.0000</t>
+          <t>0.5174±0.0073</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>0.5295±0.0000</t>
+          <t>0.5434±0.0147</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
         <is>
-          <t>0.5143±0.0000</t>
+          <t>0.5161±0.0014</t>
         </is>
       </c>
     </row>
@@ -1360,62 +1360,62 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.6797±0.0000</t>
+          <t>0.6790±0.0002</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.6795±0.0000</t>
+          <t>0.6795±0.0001</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.6795±0.0000</t>
+          <t>0.6791±0.0006</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.6795±0.0000</t>
+          <t>0.6783±0.0008</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.6794±0.0000</t>
+          <t>0.6812±0.0021</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.6795±0.0000</t>
+          <t>0.6789±0.0006</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.6794±0.0000</t>
+          <t>0.6789±0.0006</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.6794±0.0000</t>
+          <t>0.6789±0.0006</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0.6794±0.0000</t>
+          <t>0.6789±0.0006</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0.6794±0.0000</t>
+          <t>0.6792±0.0003</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>0.6736±0.0000</t>
+          <t>0.6530±0.0193</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>0.6794±0.0000</t>
+          <t>0.6793±0.0001</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1425,387 +1425,387 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>0.6795±0.0000</t>
+          <t>0.6782±0.0016</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>0.6731±0.0000</t>
+          <t>0.6792±0.0004</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>0.6794±0.0000</t>
+          <t>0.6754±0.0038</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>0.6792±0.0000</t>
+          <t>0.6775±0.0025</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.6793±0.0000</t>
+          <t>0.6791±0.0004</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>0.6796±0.0000</t>
+          <t>0.6790±0.0001</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>0.6792±0.0000</t>
+          <t>0.6784±0.0006</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>0.6792±0.0000</t>
+          <t>0.6784±0.0006</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.6792±0.0000</t>
+          <t>0.6784±0.0006</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>0.6794±0.0000</t>
+          <t>0.6801±0.0017</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>0.6795±0.0000</t>
+          <t>0.6795±0.0002</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.6790±0.0000</t>
+          <t>0.6789±0.0004</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>0.0005±0.0000</t>
+          <t>0.0041±0.0018</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>0.6729±0.0000</t>
+          <t>0.6761±0.0026</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>0.6796±0.0000</t>
+          <t>0.6778±0.0055</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>0.6794±0.0000</t>
+          <t>0.6678±0.0060</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.6795±0.0000</t>
+          <t>0.6787±0.0012</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.6758±0.0000</t>
+          <t>0.6751±0.0052</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.6788±0.0000</t>
+          <t>0.6778±0.0015</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>0.6760±0.0000</t>
+          <t>0.6747±0.0018</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>0.6760±0.0000</t>
+          <t>0.6747±0.0018</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>0.6760±0.0000</t>
+          <t>0.6747±0.0018</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>0.6776±0.0000</t>
+          <t>0.6794±0.0003</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>0.6707±0.0000</t>
+          <t>0.6598±0.0073</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>0.6743±0.0000</t>
+          <t>0.6759±0.0030</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
+          <t>0.0021±0.0018</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>0.6760±0.0041</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>0.6705±0.0066</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>0.6724±0.0023</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>0.6729±0.0048</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>0.6762±0.0036</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>0.6649±0.0112</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>0.6788±0.0004</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>0.6788±0.0004</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>0.6788±0.0004</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>0.6724±0.0020</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>0.6727±0.0010</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>0.6639±0.0069</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
           <t>0.0000±0.0000</t>
         </is>
       </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>0.6684±0.0000</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>0.6792±0.0000</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>0.6781±0.0000</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>0.6706±0.0000</t>
-        </is>
-      </c>
-      <c r="AT3" t="inlineStr">
-        <is>
-          <t>0.6695±0.0000</t>
-        </is>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>0.6664±0.0000</t>
-        </is>
-      </c>
-      <c r="AV3" t="inlineStr">
-        <is>
-          <t>0.6678±0.0000</t>
-        </is>
-      </c>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>0.6678±0.0000</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>0.6678±0.0000</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>0.6694±0.0000</t>
-        </is>
-      </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>0.6760±0.0000</t>
-        </is>
-      </c>
-      <c r="BA3" t="inlineStr">
-        <is>
-          <t>0.6609±0.0000</t>
-        </is>
-      </c>
-      <c r="BB3" t="inlineStr">
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>0.6779±0.0011</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>0.6795±0.0001</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>0.6752±0.0037</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>0.6782±0.0009</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>0.6785±0.0012</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>0.6790±0.0005</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>0.6781±0.0013</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>0.6781±0.0013</t>
+        </is>
+      </c>
+      <c r="BK3" t="inlineStr">
+        <is>
+          <t>0.6781±0.0013</t>
+        </is>
+      </c>
+      <c r="BL3" t="inlineStr">
+        <is>
+          <t>0.6791±0.0005</t>
+        </is>
+      </c>
+      <c r="BM3" t="inlineStr">
+        <is>
+          <t>0.6795±0.0002</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
+        <is>
+          <t>0.6777±0.0021</t>
+        </is>
+      </c>
+      <c r="BO3" t="inlineStr">
         <is>
           <t>0.0000±0.0000</t>
         </is>
       </c>
-      <c r="BC3" t="inlineStr">
-        <is>
-          <t>0.6795±0.0000</t>
-        </is>
-      </c>
-      <c r="BD3" t="inlineStr">
-        <is>
-          <t>0.6795±0.0000</t>
-        </is>
-      </c>
-      <c r="BE3" t="inlineStr">
-        <is>
-          <t>0.6794±0.0000</t>
-        </is>
-      </c>
-      <c r="BF3" t="inlineStr">
-        <is>
-          <t>0.6796±0.0000</t>
-        </is>
-      </c>
-      <c r="BG3" t="inlineStr">
-        <is>
-          <t>0.6795±0.0000</t>
-        </is>
-      </c>
-      <c r="BH3" t="inlineStr">
-        <is>
-          <t>0.6796±0.0000</t>
-        </is>
-      </c>
-      <c r="BI3" t="inlineStr">
-        <is>
-          <t>0.6795±0.0000</t>
-        </is>
-      </c>
-      <c r="BJ3" t="inlineStr">
-        <is>
-          <t>0.6795±0.0000</t>
-        </is>
-      </c>
-      <c r="BK3" t="inlineStr">
-        <is>
-          <t>0.6795±0.0000</t>
-        </is>
-      </c>
-      <c r="BL3" t="inlineStr">
-        <is>
-          <t>0.6796±0.0000</t>
-        </is>
-      </c>
-      <c r="BM3" t="inlineStr">
-        <is>
-          <t>0.6794±0.0000</t>
-        </is>
-      </c>
-      <c r="BN3" t="inlineStr">
-        <is>
-          <t>0.6795±0.0000</t>
-        </is>
-      </c>
-      <c r="BO3" t="inlineStr">
+      <c r="BP3" t="inlineStr">
+        <is>
+          <t>0.6776±0.0012</t>
+        </is>
+      </c>
+      <c r="BQ3" t="inlineStr">
+        <is>
+          <t>0.6795±0.0002</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr">
+        <is>
+          <t>0.6755±0.0056</t>
+        </is>
+      </c>
+      <c r="BS3" t="inlineStr">
+        <is>
+          <t>0.6785±0.0008</t>
+        </is>
+      </c>
+      <c r="BT3" t="inlineStr">
+        <is>
+          <t>0.6789±0.0004</t>
+        </is>
+      </c>
+      <c r="BU3" t="inlineStr">
+        <is>
+          <t>0.6777±0.0014</t>
+        </is>
+      </c>
+      <c r="BV3" t="inlineStr">
+        <is>
+          <t>0.6800±0.0010</t>
+        </is>
+      </c>
+      <c r="BW3" t="inlineStr">
+        <is>
+          <t>0.6799±0.0010</t>
+        </is>
+      </c>
+      <c r="BX3" t="inlineStr">
+        <is>
+          <t>0.6799±0.0010</t>
+        </is>
+      </c>
+      <c r="BY3" t="inlineStr">
+        <is>
+          <t>0.6794±0.0003</t>
+        </is>
+      </c>
+      <c r="BZ3" t="inlineStr">
+        <is>
+          <t>0.6735±0.0043</t>
+        </is>
+      </c>
+      <c r="CA3" t="inlineStr">
+        <is>
+          <t>0.6784±0.0010</t>
+        </is>
+      </c>
+      <c r="CB3" t="inlineStr">
         <is>
           <t>0.0000±0.0000</t>
         </is>
       </c>
-      <c r="BP3" t="inlineStr">
-        <is>
-          <t>0.6795±0.0000</t>
-        </is>
-      </c>
-      <c r="BQ3" t="inlineStr">
-        <is>
-          <t>0.6795±0.0000</t>
-        </is>
-      </c>
-      <c r="BR3" t="inlineStr">
-        <is>
-          <t>0.6794±0.0000</t>
-        </is>
-      </c>
-      <c r="BS3" t="inlineStr">
-        <is>
-          <t>0.6795±0.0000</t>
-        </is>
-      </c>
-      <c r="BT3" t="inlineStr">
-        <is>
-          <t>0.6794±0.0000</t>
-        </is>
-      </c>
-      <c r="BU3" t="inlineStr">
-        <is>
-          <t>0.6796±0.0000</t>
-        </is>
-      </c>
-      <c r="BV3" t="inlineStr">
-        <is>
-          <t>0.6794±0.0000</t>
-        </is>
-      </c>
-      <c r="BW3" t="inlineStr">
-        <is>
-          <t>0.6794±0.0000</t>
-        </is>
-      </c>
-      <c r="BX3" t="inlineStr">
-        <is>
-          <t>0.6794±0.0000</t>
-        </is>
-      </c>
-      <c r="BY3" t="inlineStr">
-        <is>
-          <t>0.6796±0.0000</t>
-        </is>
-      </c>
-      <c r="BZ3" t="inlineStr">
-        <is>
-          <t>0.6795±0.0000</t>
-        </is>
-      </c>
-      <c r="CA3" t="inlineStr">
-        <is>
-          <t>0.6794±0.0000</t>
-        </is>
-      </c>
-      <c r="CB3" t="inlineStr">
-        <is>
-          <t>0.0000±0.0000</t>
-        </is>
-      </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>0.6735±0.0000</t>
+          <t>0.6737±0.0017</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>0.6788±0.0000</t>
+          <t>0.6724±0.0050</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>0.6793±0.0000</t>
+          <t>0.6744±0.0001</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>0.6781±0.0000</t>
+          <t>0.6759±0.0017</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>0.6785±0.0000</t>
+          <t>0.6789±0.0010</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>0.6754±0.0000</t>
+          <t>0.6750±0.0021</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>0.6758±0.0000</t>
+          <t>0.6773±0.0008</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
         <is>
-          <t>0.6758±0.0000</t>
+          <t>0.6773±0.0008</t>
         </is>
       </c>
       <c r="CK3" t="inlineStr">
         <is>
-          <t>0.6758±0.0000</t>
+          <t>0.6773±0.0008</t>
         </is>
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>0.6679±0.0000</t>
+          <t>0.6731±0.0040</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>0.6654±0.0000</t>
+          <t>0.6572±0.0128</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
         <is>
-          <t>0.6765±0.0000</t>
+          <t>0.6766±0.0005</t>
         </is>
       </c>
     </row>
@@ -1817,457 +1817,457 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.6190±0.0000</t>
+          <t>0.6480±0.0112</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.4580±0.0000</t>
+          <t>0.6089±0.0209</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.4999±0.0000</t>
+          <t>0.5000±0.0000</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.4993±0.0000</t>
+          <t>0.5378±0.0543</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.4996±0.0000</t>
+          <t>0.6340±0.0139</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.4998±0.0000</t>
+          <t>0.5815±0.0175</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.4483±0.0000</t>
+          <t>0.5713±0.0168</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
+          <t>0.6125±0.0795</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>0.6125±0.0795</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0.6125±0.0795</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>0.5396±0.0168</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>0.5599±0.0032</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0.5583±0.0427</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0.4522±0.0875</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>0.5497±0.0446</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0.5155±0.0190</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>0.5533±0.0386</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>0.5409±0.0237</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>0.5539±0.0071</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>0.5846±0.0394</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>0.5913±0.0343</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0.5913±0.0343</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>0.5913±0.0343</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>0.5373±0.0513</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>0.6055±0.0022</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>0.5571±0.0167</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>0.4730±0.0654</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>0.5294±0.0098</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>0.5301±0.0255</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>0.5496±0.0101</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>0.5138±0.0038</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>0.5206±0.0188</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>0.4945±0.0120</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>0.5404±0.0101</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>0.5404±0.0101</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>0.5404±0.0101</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>0.4986±0.0116</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>0.5875±0.0048</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>0.5505±0.0165</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>0.4760±0.1410</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>0.5486±0.0030</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>0.5672±0.0021</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>0.5534±0.0191</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>0.5545±0.0133</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>0.5453±0.0151</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>0.5452±0.0047</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>0.5594±0.0054</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>0.5594±0.0054</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>0.5594±0.0054</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>0.5349±0.0137</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>0.5572±0.0031</t>
+        </is>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>0.5563±0.0021</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>0.6393±0.0074</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>0.5529±0.0503</t>
+        </is>
+      </c>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>0.5000±0.0001</t>
+        </is>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>0.5982±0.0536</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>0.6031±0.0187</t>
+        </is>
+      </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>0.6056±0.0363</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>0.5925±0.0259</t>
+        </is>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
+          <t>0.5966±0.0211</t>
+        </is>
+      </c>
+      <c r="BJ4" t="inlineStr">
+        <is>
+          <t>0.5966±0.0211</t>
+        </is>
+      </c>
+      <c r="BK4" t="inlineStr">
+        <is>
+          <t>0.5966±0.0211</t>
+        </is>
+      </c>
+      <c r="BL4" t="inlineStr">
+        <is>
+          <t>0.5898±0.0377</t>
+        </is>
+      </c>
+      <c r="BM4" t="inlineStr">
+        <is>
+          <t>0.5569±0.0014</t>
+        </is>
+      </c>
+      <c r="BN4" t="inlineStr">
+        <is>
+          <t>0.5823±0.0208</t>
+        </is>
+      </c>
+      <c r="BO4" t="inlineStr">
+        <is>
+          <t>0.6332±0.0076</t>
+        </is>
+      </c>
+      <c r="BP4" t="inlineStr">
+        <is>
+          <t>0.5936±0.0183</t>
+        </is>
+      </c>
+      <c r="BQ4" t="inlineStr">
+        <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="BR4" t="inlineStr">
+        <is>
+          <t>0.5370±0.0520</t>
+        </is>
+      </c>
+      <c r="BS4" t="inlineStr">
+        <is>
+          <t>0.5659±0.0489</t>
+        </is>
+      </c>
+      <c r="BT4" t="inlineStr">
+        <is>
+          <t>0.6025±0.0144</t>
+        </is>
+      </c>
+      <c r="BU4" t="inlineStr">
+        <is>
+          <t>0.5878±0.0411</t>
+        </is>
+      </c>
+      <c r="BV4" t="inlineStr">
+        <is>
+          <t>0.5946±0.0177</t>
+        </is>
+      </c>
+      <c r="BW4" t="inlineStr">
+        <is>
+          <t>0.5947±0.0177</t>
+        </is>
+      </c>
+      <c r="BX4" t="inlineStr">
+        <is>
+          <t>0.5947±0.0177</t>
+        </is>
+      </c>
+      <c r="BY4" t="inlineStr">
+        <is>
+          <t>0.5423±0.0350</t>
+        </is>
+      </c>
+      <c r="BZ4" t="inlineStr">
+        <is>
+          <t>0.5627±0.0034</t>
+        </is>
+      </c>
+      <c r="CA4" t="inlineStr">
+        <is>
+          <t>0.5372±0.0320</t>
+        </is>
+      </c>
+      <c r="CB4" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>0.4471±0.0000</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>0.5700±0.0000</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0.4171±0.0000</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>0.4796±0.0000</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0.4994±0.0000</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>0.4989±0.0000</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>0.5458±0.0000</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>0.5702±0.0000</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>0.5104±0.0000</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>0.5287±0.0000</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0.5287±0.0000</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>0.5287±0.0000</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>0.5118±0.0000</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>0.6127±0.0000</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>0.5493±0.0000</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>0.4722±0.0000</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>0.4957±0.0000</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>0.5003±0.0000</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>0.4999±0.0000</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>0.5044±0.0000</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>0.5117±0.0000</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>0.4766±0.0000</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>0.5106±0.0000</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>0.5106±0.0000</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>0.5106±0.0000</t>
-        </is>
-      </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>0.5058±0.0000</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>0.5884±0.0000</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>0.5064±0.0000</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>0.5236±0.0000</t>
-        </is>
-      </c>
-      <c r="AP4" t="inlineStr">
-        <is>
-          <t>0.5460±0.0000</t>
-        </is>
-      </c>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>0.4998±0.0000</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>0.5032±0.0000</t>
-        </is>
-      </c>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>0.5314±0.0000</t>
-        </is>
-      </c>
-      <c r="AT4" t="inlineStr">
-        <is>
-          <t>0.5294±0.0000</t>
-        </is>
-      </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>0.5473±0.0000</t>
-        </is>
-      </c>
-      <c r="AV4" t="inlineStr">
-        <is>
-          <t>0.5301±0.0000</t>
-        </is>
-      </c>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>0.5301±0.0000</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>0.5301±0.0000</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>0.5470±0.0000</t>
-        </is>
-      </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>0.5952±0.0000</t>
-        </is>
-      </c>
-      <c r="BA4" t="inlineStr">
-        <is>
-          <t>0.5291±0.0000</t>
-        </is>
-      </c>
-      <c r="BB4" t="inlineStr">
-        <is>
-          <t>0.6337±0.0000</t>
-        </is>
-      </c>
-      <c r="BC4" t="inlineStr">
-        <is>
-          <t>0.4893±0.0000</t>
-        </is>
-      </c>
-      <c r="BD4" t="inlineStr">
-        <is>
-          <t>0.4999±0.0000</t>
-        </is>
-      </c>
-      <c r="BE4" t="inlineStr">
-        <is>
-          <t>0.4957±0.0000</t>
-        </is>
-      </c>
-      <c r="BF4" t="inlineStr">
-        <is>
-          <t>0.4998±0.0000</t>
-        </is>
-      </c>
-      <c r="BG4" t="inlineStr">
-        <is>
-          <t>0.4996±0.0000</t>
-        </is>
-      </c>
-      <c r="BH4" t="inlineStr">
-        <is>
-          <t>0.4548±0.0000</t>
-        </is>
-      </c>
-      <c r="BI4" t="inlineStr">
-        <is>
-          <t>0.4993±0.0000</t>
-        </is>
-      </c>
-      <c r="BJ4" t="inlineStr">
-        <is>
-          <t>0.4993±0.0000</t>
-        </is>
-      </c>
-      <c r="BK4" t="inlineStr">
-        <is>
-          <t>0.4993±0.0000</t>
-        </is>
-      </c>
-      <c r="BL4" t="inlineStr">
-        <is>
-          <t>0.4596±0.0000</t>
-        </is>
-      </c>
-      <c r="BM4" t="inlineStr">
-        <is>
-          <t>0.5563±0.0000</t>
-        </is>
-      </c>
-      <c r="BN4" t="inlineStr">
-        <is>
-          <t>0.4996±0.0000</t>
-        </is>
-      </c>
-      <c r="BO4" t="inlineStr">
-        <is>
-          <t>0.6379±0.0000</t>
-        </is>
-      </c>
-      <c r="BP4" t="inlineStr">
-        <is>
-          <t>0.4554±0.0000</t>
-        </is>
-      </c>
-      <c r="BQ4" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BR4" t="inlineStr">
-        <is>
-          <t>0.4999±0.0000</t>
-        </is>
-      </c>
-      <c r="BS4" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BT4" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BU4" t="inlineStr">
-        <is>
-          <t>0.4539±0.0000</t>
-        </is>
-      </c>
-      <c r="BV4" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BW4" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BX4" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BY4" t="inlineStr">
-        <is>
-          <t>0.4463±0.0000</t>
-        </is>
-      </c>
-      <c r="BZ4" t="inlineStr">
-        <is>
-          <t>0.5584±0.0000</t>
-        </is>
-      </c>
-      <c r="CA4" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="CB4" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>0.5353±0.0000</t>
+          <t>0.5989±0.0331</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>0.4993±0.0000</t>
+          <t>0.5126±0.0160</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>0.5002±0.0000</t>
+          <t>0.5702±0.0086</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>0.5186±0.0000</t>
+          <t>0.5652±0.0170</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>0.5794±0.0000</t>
+          <t>0.5962±0.0370</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>0.5789±0.0000</t>
+          <t>0.5573±0.0460</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>0.5577±0.0000</t>
+          <t>0.5820±0.0141</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
         <is>
-          <t>0.5577±0.0000</t>
+          <t>0.5820±0.0141</t>
         </is>
       </c>
       <c r="CK4" t="inlineStr">
         <is>
-          <t>0.5577±0.0000</t>
+          <t>0.5820±0.0141</t>
         </is>
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>0.5410±0.0000</t>
+          <t>0.5902±0.0155</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>0.5664±0.0000</t>
+          <t>0.5749±0.0026</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
         <is>
-          <t>0.5432±0.0000</t>
+          <t>0.5852±0.0119</t>
         </is>
       </c>
     </row>
@@ -2279,457 +2279,457 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.6195±0.0000</t>
+          <t>0.6596±0.0130</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.4851±0.0000</t>
+          <t>0.5957±0.0160</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.5145±0.0000</t>
+          <t>0.5146±0.0002</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.5142±0.0000</t>
+          <t>0.5555±0.0584</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0.5144±0.0000</t>
+          <t>0.6090±0.0172</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.5145±0.0000</t>
+          <t>0.5625±0.0109</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.4808±0.0000</t>
+          <t>0.5566±0.0142</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.5145±0.0000</t>
+          <t>0.6206±0.0751</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.5145±0.0000</t>
+          <t>0.6206±0.0751</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0.5145±0.0000</t>
+          <t>0.6206±0.0751</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0.4785±0.0000</t>
+          <t>0.5322±0.0129</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>0.5645±0.0000</t>
+          <t>0.5576±0.0014</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>0.5146±0.0000</t>
+          <t>0.5534±0.0286</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>0.4416±0.0000</t>
+          <t>0.4757±0.0566</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>0.5007±0.0000</t>
+          <t>0.5397±0.0276</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>0.5137±0.0000</t>
+          <t>0.5204±0.0067</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>0.5140±0.0000</t>
+          <t>0.5600±0.0319</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>0.5388±0.0000</t>
+          <t>0.5437±0.0120</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.5630±0.0000</t>
+          <t>0.5483±0.0098</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>0.5202±0.0000</t>
+          <t>0.5668±0.0416</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>0.5445±0.0000</t>
+          <t>0.5862±0.0327</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.5445±0.0000</t>
+          <t>0.5862±0.0327</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.5445±0.0000</t>
+          <t>0.5862±0.0327</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>0.5219±0.0000</t>
+          <t>0.5306±0.0326</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.5902±0.0000</t>
+          <t>0.5871±0.0013</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.5503±0.0000</t>
+          <t>0.5566±0.0123</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>0.4761±0.0000</t>
+          <t>0.4939±0.0354</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>0.5087±0.0000</t>
+          <t>0.5307±0.0045</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>0.5147±0.0000</t>
+          <t>0.5300±0.0150</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>0.5145±0.0000</t>
+          <t>0.5502±0.0104</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.5168±0.0000</t>
+          <t>0.5217±0.0020</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>0.5206±0.0000</t>
+          <t>0.5322±0.0193</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.5104±0.0000</t>
+          <t>0.5139±0.0132</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>0.5200±0.0000</t>
+          <t>0.5498±0.0048</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>0.5200±0.0000</t>
+          <t>0.5498±0.0048</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.5200±0.0000</t>
+          <t>0.5498±0.0048</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>0.5279±0.0000</t>
+          <t>0.5119±0.0033</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>0.5787±0.0000</t>
+          <t>0.5778±0.0045</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>0.5178±0.0000</t>
+          <t>0.5546±0.0183</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>0.5230±0.0000</t>
+          <t>0.4958±0.0783</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>0.5298±0.0000</t>
+          <t>0.5437±0.0006</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.5145±0.0000</t>
+          <t>0.5562±0.0020</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.5162±0.0000</t>
+          <t>0.5573±0.0145</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.5314±0.0000</t>
+          <t>0.5485±0.0055</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.5302±0.0000</t>
+          <t>0.5428±0.0083</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>0.5322±0.0000</t>
+          <t>0.5411±0.0068</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>0.5328±0.0000</t>
+          <t>0.5474±0.0059</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>0.5328±0.0000</t>
+          <t>0.5474±0.0059</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>0.5328±0.0000</t>
+          <t>0.5474±0.0059</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>0.5390±0.0000</t>
+          <t>0.5322±0.0105</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>0.5825±0.0000</t>
+          <t>0.5579±0.0039</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>0.5369±0.0000</t>
+          <t>0.5499±0.0031</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>0.6397±0.0000</t>
+          <t>0.6493±0.0068</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>0.5021±0.0000</t>
+          <t>0.5469±0.0470</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>0.5145±0.0000</t>
+          <t>0.5146±0.0002</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>0.5124±0.0000</t>
+          <t>0.6103±0.0658</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>0.5144±0.0000</t>
+          <t>0.5920±0.0143</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>0.5144±0.0000</t>
+          <t>0.5887±0.0441</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>0.4842±0.0000</t>
+          <t>0.5739±0.0156</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>0.5142±0.0000</t>
+          <t>0.5724±0.0244</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>0.5142±0.0000</t>
+          <t>0.5724±0.0244</t>
         </is>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>0.5142±0.0000</t>
+          <t>0.5724±0.0244</t>
         </is>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>0.4862±0.0000</t>
+          <t>0.5672±0.0246</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.5525±0.0000</t>
+          <t>0.5528±0.0021</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>0.5144±0.0000</t>
+          <t>0.5741±0.0223</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>0.6449±0.0000</t>
+          <t>0.6426±0.0077</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>0.4851±0.0000</t>
+          <t>0.5807±0.0202</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>0.5146±0.0000</t>
+          <t>0.5146±0.0002</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>0.5145±0.0000</t>
+          <t>0.5475±0.0464</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>0.5146±0.0000</t>
+          <t>0.5514±0.0297</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>0.5146±0.0000</t>
+          <t>0.5781±0.0192</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>0.4826±0.0000</t>
+          <t>0.5713±0.0262</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>0.5146±0.0000</t>
+          <t>0.5730±0.0266</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
         <is>
-          <t>0.5146±0.0000</t>
+          <t>0.5730±0.0266</t>
         </is>
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>0.5146±0.0000</t>
+          <t>0.5730±0.0266</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>0.4795±0.0000</t>
+          <t>0.5305±0.0224</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>0.5548±0.0000</t>
+          <t>0.5586±0.0030</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
         <is>
-          <t>0.5146±0.0000</t>
+          <t>0.5336±0.0219</t>
         </is>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>0.5146±0.0000</t>
+          <t>0.5146±0.0002</t>
         </is>
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>0.5441±0.0000</t>
+          <t>0.5877±0.0246</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>0.5142±0.0000</t>
+          <t>0.5212±0.0085</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>0.5147±0.0000</t>
+          <t>0.5723±0.0035</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>0.5243±0.0000</t>
+          <t>0.5581±0.0112</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>0.5564±0.0000</t>
+          <t>0.5813±0.0284</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>0.5730±0.0000</t>
+          <t>0.5594±0.0323</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>0.5489±0.0000</t>
+          <t>0.5718±0.0190</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
         <is>
-          <t>0.5489±0.0000</t>
+          <t>0.5718±0.0190</t>
         </is>
       </c>
       <c r="CK5" t="inlineStr">
         <is>
-          <t>0.5489±0.0000</t>
+          <t>0.5718±0.0190</t>
         </is>
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>0.5423±0.0000</t>
+          <t>0.5792±0.0119</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>0.5621±0.0000</t>
+          <t>0.5675±0.0048</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
         <is>
-          <t>0.5479±0.0000</t>
+          <t>0.5706±0.0089</t>
         </is>
       </c>
     </row>
